--- a/myapp/Cards.xlsx
+++ b/myapp/Cards.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="924">
   <si>
     <t>Name</t>
   </si>
@@ -2774,6 +2774,15 @@
   </si>
   <si>
     <t>DLL-64.jpg</t>
+  </si>
+  <si>
+    <t>New Item for Jack</t>
+  </si>
+  <si>
+    <t>DLL-65</t>
+  </si>
+  <si>
+    <t>DLL-65.jpg</t>
   </si>
 </sst>
 </file>
@@ -3935,7 +3944,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I211"/>
+  <dimension ref="A1:I212"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="22.2578" style="1" customWidth="1"/>
@@ -10196,6 +10205,36 @@
         <v>860</v>
       </c>
     </row>
+    <row r="212" ht="15.35" customHeight="1">
+      <c r="A212" t="s" s="2">
+        <v>921</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>922</v>
+      </c>
+      <c r="C212" t="s" s="2">
+        <f>B212&amp;".jpg"</f>
+        <v>923</v>
+      </c>
+      <c r="D212" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="E212" s="3">
+        <v>316</v>
+      </c>
+      <c r="F212" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G212" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H212" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="I212" t="s" s="2">
+        <v>860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
